--- a/AAII_Financials/Quarterly/PGRU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGRU_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>PGRU</t>
   </si>
@@ -656,131 +656,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>27400</v>
+        <v>81300</v>
       </c>
       <c r="E8" s="3">
-        <v>24200</v>
+        <v>27600</v>
       </c>
       <c r="F8" s="3">
-        <v>29800</v>
+        <v>24400</v>
       </c>
       <c r="G8" s="3">
-        <v>25700</v>
+        <v>30000</v>
       </c>
       <c r="H8" s="3">
-        <v>24500</v>
+        <v>25900</v>
       </c>
       <c r="I8" s="3">
-        <v>20900</v>
+        <v>24700</v>
       </c>
       <c r="J8" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K8" s="3">
         <v>74800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>31800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>60700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>26300</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,8 +833,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,102 +1003,111 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6300</v>
+        <v>4500</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1100</v>
       </c>
-      <c r="I14" s="3">
-        <v>91200</v>
-      </c>
       <c r="J14" s="3">
+        <v>91900</v>
+      </c>
+      <c r="K14" s="3">
         <v>6100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E15" s="3">
         <v>4300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4400</v>
       </c>
-      <c r="F15" s="3">
-        <v>4000</v>
-      </c>
       <c r="G15" s="3">
-        <v>3600</v>
+        <v>4100</v>
       </c>
       <c r="H15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I15" s="3">
         <v>4400</v>
       </c>
-      <c r="I15" s="3">
-        <v>3600</v>
-      </c>
       <c r="J15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K15" s="3">
         <v>10400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3500</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>34100</v>
+        <v>94300</v>
       </c>
       <c r="E17" s="3">
-        <v>29300</v>
+        <v>34300</v>
       </c>
       <c r="F17" s="3">
-        <v>31300</v>
+        <v>29600</v>
       </c>
       <c r="G17" s="3">
-        <v>27900</v>
+        <v>31900</v>
       </c>
       <c r="H17" s="3">
-        <v>28300</v>
+        <v>28100</v>
       </c>
       <c r="I17" s="3">
-        <v>117700</v>
+        <v>28500</v>
       </c>
       <c r="J17" s="3">
+        <v>118700</v>
+      </c>
+      <c r="K17" s="3">
         <v>110600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>69700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27800</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6700</v>
       </c>
-      <c r="E18" s="3">
-        <v>-5100</v>
-      </c>
       <c r="F18" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-96800</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-35900</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,102 +1242,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>2100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2400</v>
       </c>
-      <c r="F20" s="3">
-        <v>-2000</v>
-      </c>
       <c r="G20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="H20" s="3">
-        <v>6600</v>
-      </c>
       <c r="I20" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J20" s="3">
         <v>7500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-103500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="H21" s="3">
-        <v>7200</v>
-      </c>
       <c r="I21" s="3">
-        <v>-85600</v>
+        <v>7300</v>
       </c>
       <c r="J21" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-129000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-107800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1350,102 +1390,111 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4600</v>
       </c>
-      <c r="E23" s="3">
-        <v>-7500</v>
-      </c>
       <c r="F23" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="G23" s="3">
         <v>-3500</v>
       </c>
-      <c r="G23" s="3">
-        <v>-5100</v>
-      </c>
       <c r="H23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I23" s="3">
         <v>2800</v>
       </c>
-      <c r="I23" s="3">
-        <v>-89300</v>
-      </c>
       <c r="J23" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="K23" s="3">
         <v>-139400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-111500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>400</v>
       </c>
       <c r="G24" s="3">
         <v>400</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4800</v>
       </c>
-      <c r="E26" s="3">
-        <v>-7600</v>
-      </c>
       <c r="F26" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="G26" s="3">
         <v>-3900</v>
       </c>
-      <c r="G26" s="3">
-        <v>-5500</v>
-      </c>
       <c r="H26" s="3">
-        <v>2800</v>
+        <v>-5600</v>
       </c>
       <c r="I26" s="3">
-        <v>-89300</v>
+        <v>2900</v>
       </c>
       <c r="J26" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-139100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-111700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1700</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4800</v>
       </c>
-      <c r="E27" s="3">
-        <v>-7600</v>
-      </c>
       <c r="F27" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="G27" s="3">
         <v>-3900</v>
       </c>
-      <c r="G27" s="3">
-        <v>-5500</v>
-      </c>
       <c r="H27" s="3">
-        <v>2800</v>
+        <v>-5600</v>
       </c>
       <c r="I27" s="3">
-        <v>-89300</v>
+        <v>2900</v>
       </c>
       <c r="J27" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-139100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-111700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1840,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2400</v>
       </c>
-      <c r="F32" s="3">
-        <v>2000</v>
-      </c>
       <c r="G32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="H32" s="3">
-        <v>-6600</v>
-      </c>
       <c r="I32" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="J32" s="3">
         <v>-7500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>103500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4800</v>
       </c>
-      <c r="E33" s="3">
-        <v>-7600</v>
-      </c>
       <c r="F33" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="G33" s="3">
         <v>-3900</v>
       </c>
-      <c r="G33" s="3">
-        <v>-5500</v>
-      </c>
       <c r="H33" s="3">
-        <v>2800</v>
+        <v>-5600</v>
       </c>
       <c r="I33" s="3">
-        <v>-89300</v>
+        <v>2900</v>
       </c>
       <c r="J33" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-139100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-111700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4800</v>
       </c>
-      <c r="E35" s="3">
-        <v>-7600</v>
-      </c>
       <c r="F35" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="G35" s="3">
         <v>-3900</v>
       </c>
-      <c r="G35" s="3">
-        <v>-5500</v>
-      </c>
       <c r="H35" s="3">
-        <v>2800</v>
+        <v>-5600</v>
       </c>
       <c r="I35" s="3">
-        <v>-89300</v>
+        <v>2900</v>
       </c>
       <c r="J35" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-139100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-111700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,38 +2137,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>224000</v>
+        <v>237000</v>
       </c>
       <c r="E41" s="3">
-        <v>218500</v>
+        <v>225900</v>
       </c>
       <c r="F41" s="3">
-        <v>229600</v>
+        <v>220400</v>
       </c>
       <c r="G41" s="3">
-        <v>252100</v>
+        <v>231500</v>
       </c>
       <c r="H41" s="3">
-        <v>273700</v>
+        <v>254300</v>
       </c>
       <c r="I41" s="3">
-        <v>274300</v>
+        <v>276100</v>
       </c>
       <c r="J41" s="3">
+        <v>276600</v>
+      </c>
+      <c r="K41" s="3">
         <v>52100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>57800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2098,8 +2185,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,8 +2235,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2183,8 +2276,8 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
+      <c r="O43" s="3">
+        <v>0</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
@@ -2192,8 +2285,11 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2239,8 +2335,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2286,38 +2385,41 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>236900</v>
+        <v>249800</v>
       </c>
       <c r="E46" s="3">
-        <v>231900</v>
+        <v>238900</v>
       </c>
       <c r="F46" s="3">
-        <v>243000</v>
+        <v>233800</v>
       </c>
       <c r="G46" s="3">
-        <v>264600</v>
+        <v>245100</v>
       </c>
       <c r="H46" s="3">
-        <v>287900</v>
+        <v>266800</v>
       </c>
       <c r="I46" s="3">
-        <v>285800</v>
+        <v>290300</v>
       </c>
       <c r="J46" s="3">
+        <v>288300</v>
+      </c>
+      <c r="K46" s="3">
         <v>65200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>67300</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,38 +2435,41 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E47" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="F47" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G47" s="3">
         <v>3400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2500</v>
-      </c>
-      <c r="H47" s="3">
-        <v>2600</v>
       </c>
       <c r="I47" s="3">
         <v>2600</v>
       </c>
       <c r="J47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K47" s="3">
         <v>1200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2380,37 +2485,40 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>8100</v>
+        <v>8700</v>
       </c>
       <c r="E48" s="3">
-        <v>9300</v>
+        <v>8200</v>
       </c>
       <c r="F48" s="3">
-        <v>10400</v>
+        <v>9400</v>
       </c>
       <c r="G48" s="3">
-        <v>11000</v>
+        <v>10500</v>
       </c>
       <c r="H48" s="3">
-        <v>11700</v>
+        <v>11100</v>
       </c>
       <c r="I48" s="3">
-        <v>12700</v>
+        <v>11800</v>
       </c>
       <c r="J48" s="3">
-        <v>13900</v>
+        <v>12900</v>
       </c>
       <c r="K48" s="3">
         <v>13900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
+      <c r="L48" s="3">
+        <v>13900</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
@@ -2427,38 +2535,41 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>283100</v>
+        <v>286400</v>
       </c>
       <c r="E49" s="3">
-        <v>291200</v>
+        <v>285500</v>
       </c>
       <c r="F49" s="3">
-        <v>292100</v>
+        <v>293700</v>
       </c>
       <c r="G49" s="3">
-        <v>296100</v>
+        <v>294700</v>
       </c>
       <c r="H49" s="3">
-        <v>294900</v>
+        <v>298600</v>
       </c>
       <c r="I49" s="3">
-        <v>298000</v>
+        <v>297400</v>
       </c>
       <c r="J49" s="3">
+        <v>300500</v>
+      </c>
+      <c r="K49" s="3">
         <v>297800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>108200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2685,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,38 +2785,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>531200</v>
+        <v>547400</v>
       </c>
       <c r="E54" s="3">
-        <v>536000</v>
+        <v>535700</v>
       </c>
       <c r="F54" s="3">
-        <v>548900</v>
+        <v>540500</v>
       </c>
       <c r="G54" s="3">
-        <v>574200</v>
+        <v>553700</v>
       </c>
       <c r="H54" s="3">
-        <v>597100</v>
+        <v>579100</v>
       </c>
       <c r="I54" s="3">
-        <v>599200</v>
+        <v>602200</v>
       </c>
       <c r="J54" s="3">
+        <v>604300</v>
+      </c>
+      <c r="K54" s="3">
         <v>378100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>190400</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2709,8 +2835,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,38 +2877,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>20100</v>
+        <v>22100</v>
       </c>
       <c r="E57" s="3">
-        <v>17700</v>
+        <v>20200</v>
       </c>
       <c r="F57" s="3">
-        <v>22100</v>
+        <v>17800</v>
       </c>
       <c r="G57" s="3">
-        <v>18600</v>
+        <v>22300</v>
       </c>
       <c r="H57" s="3">
-        <v>32000</v>
+        <v>18800</v>
       </c>
       <c r="I57" s="3">
-        <v>35800</v>
+        <v>32300</v>
       </c>
       <c r="J57" s="3">
+        <v>36200</v>
+      </c>
+      <c r="K57" s="3">
         <v>24400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14800</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,38 +2925,41 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>3000</v>
       </c>
       <c r="G58" s="3">
         <v>3100</v>
       </c>
       <c r="H58" s="3">
-        <v>16700</v>
+        <v>3100</v>
       </c>
       <c r="I58" s="3">
-        <v>16000</v>
+        <v>16900</v>
       </c>
       <c r="J58" s="3">
+        <v>16200</v>
+      </c>
+      <c r="K58" s="3">
         <v>3400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2800</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2841,38 +2975,41 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>43700</v>
+        <v>52100</v>
       </c>
       <c r="E59" s="3">
-        <v>41700</v>
+        <v>44100</v>
       </c>
       <c r="F59" s="3">
-        <v>41100</v>
+        <v>42100</v>
       </c>
       <c r="G59" s="3">
-        <v>47900</v>
+        <v>41400</v>
       </c>
       <c r="H59" s="3">
-        <v>44000</v>
+        <v>48300</v>
       </c>
       <c r="I59" s="3">
-        <v>49100</v>
+        <v>44400</v>
       </c>
       <c r="J59" s="3">
+        <v>49500</v>
+      </c>
+      <c r="K59" s="3">
         <v>38500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>276600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2888,38 +3025,41 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>66600</v>
+        <v>77700</v>
       </c>
       <c r="E60" s="3">
-        <v>62500</v>
+        <v>67100</v>
       </c>
       <c r="F60" s="3">
-        <v>66200</v>
+        <v>63000</v>
       </c>
       <c r="G60" s="3">
-        <v>69700</v>
+        <v>66800</v>
       </c>
       <c r="H60" s="3">
-        <v>92800</v>
+        <v>70300</v>
       </c>
       <c r="I60" s="3">
-        <v>101000</v>
+        <v>93600</v>
       </c>
       <c r="J60" s="3">
+        <v>101900</v>
+      </c>
+      <c r="K60" s="3">
         <v>66400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>294200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2935,38 +3075,41 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="E61" s="3">
-        <v>5400</v>
+        <v>4900</v>
       </c>
       <c r="F61" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G61" s="3">
         <v>6200</v>
       </c>
-      <c r="G61" s="3">
-        <v>6900</v>
-      </c>
       <c r="H61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I61" s="3">
         <v>7700</v>
       </c>
-      <c r="I61" s="3">
-        <v>8600</v>
-      </c>
       <c r="J61" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K61" s="3">
         <v>21700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2982,38 +3125,41 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5600</v>
+        <v>3300</v>
       </c>
       <c r="E62" s="3">
-        <v>7100</v>
+        <v>5700</v>
       </c>
       <c r="F62" s="3">
-        <v>5700</v>
+        <v>7200</v>
       </c>
       <c r="G62" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H62" s="3">
         <v>2100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,38 +3325,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>77000</v>
+        <v>85700</v>
       </c>
       <c r="E66" s="3">
-        <v>75100</v>
+        <v>77700</v>
       </c>
       <c r="F66" s="3">
-        <v>78000</v>
+        <v>75700</v>
       </c>
       <c r="G66" s="3">
-        <v>78600</v>
+        <v>78800</v>
       </c>
       <c r="H66" s="3">
-        <v>103000</v>
+        <v>79300</v>
       </c>
       <c r="I66" s="3">
-        <v>112300</v>
+        <v>103900</v>
       </c>
       <c r="J66" s="3">
+        <v>113200</v>
+      </c>
+      <c r="K66" s="3">
         <v>90700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>318100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,8 +3375,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3357,11 +3525,11 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>44000</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,38 +3595,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-334000</v>
+        <v>-336300</v>
       </c>
       <c r="E72" s="3">
-        <v>-325600</v>
+        <v>-336800</v>
       </c>
       <c r="F72" s="3">
-        <v>-319300</v>
+        <v>-328400</v>
       </c>
       <c r="G72" s="3">
-        <v>-315200</v>
+        <v>-322000</v>
       </c>
       <c r="H72" s="3">
-        <v>-310400</v>
+        <v>-317900</v>
       </c>
       <c r="I72" s="3">
-        <v>-313600</v>
+        <v>-313100</v>
       </c>
       <c r="J72" s="3">
+        <v>-316300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-222600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-200300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3645,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,38 +3795,41 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>454200</v>
+        <v>461700</v>
       </c>
       <c r="E76" s="3">
-        <v>460900</v>
+        <v>458100</v>
       </c>
       <c r="F76" s="3">
-        <v>470800</v>
+        <v>464800</v>
       </c>
       <c r="G76" s="3">
-        <v>495500</v>
+        <v>474900</v>
       </c>
       <c r="H76" s="3">
-        <v>494000</v>
+        <v>499800</v>
       </c>
       <c r="I76" s="3">
-        <v>486900</v>
+        <v>498300</v>
       </c>
       <c r="J76" s="3">
+        <v>491100</v>
+      </c>
+      <c r="K76" s="3">
         <v>287400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-171800</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,8 +3845,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4800</v>
       </c>
-      <c r="E81" s="3">
-        <v>-7600</v>
-      </c>
       <c r="F81" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="G81" s="3">
         <v>-3900</v>
       </c>
-      <c r="G81" s="3">
-        <v>-5500</v>
-      </c>
       <c r="H81" s="3">
-        <v>2800</v>
+        <v>-5600</v>
       </c>
       <c r="I81" s="3">
-        <v>-89300</v>
+        <v>2900</v>
       </c>
       <c r="J81" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-139100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-111700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4022,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E83" s="3">
         <v>4300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4400</v>
       </c>
-      <c r="F83" s="3">
-        <v>4000</v>
-      </c>
       <c r="G83" s="3">
-        <v>3600</v>
+        <v>4100</v>
       </c>
       <c r="H83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I83" s="3">
         <v>4400</v>
       </c>
-      <c r="I83" s="3">
-        <v>3600</v>
-      </c>
       <c r="J83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K83" s="3">
         <v>10400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>8100</v>
+        <v>20400</v>
       </c>
       <c r="E89" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3700</v>
       </c>
-      <c r="F89" s="3">
-        <v>-12300</v>
-      </c>
       <c r="G89" s="3">
-        <v>-4300</v>
+        <v>-12500</v>
       </c>
       <c r="H89" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="I89" s="3">
         <v>5400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4392,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-5000</v>
       </c>
-      <c r="E94" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13500</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,72 +4810,78 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="G100" s="3">
-        <v>-14100</v>
-      </c>
       <c r="H100" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
-        <v>230800</v>
-      </c>
       <c r="J100" s="3">
+        <v>232700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-7400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>65400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>18800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E101" s="3">
         <v>3400</v>
       </c>
-      <c r="E101" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+      <c r="F101" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="H101" s="3">
+        <v>3900</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -4640,8 +4889,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4661,8 +4910,11 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4670,42 +4922,45 @@
         <v>5500</v>
       </c>
       <c r="E102" s="3">
-        <v>-11000</v>
+        <v>5500</v>
       </c>
       <c r="F102" s="3">
-        <v>-22600</v>
+        <v>-11100</v>
       </c>
       <c r="G102" s="3">
-        <v>-21600</v>
+        <v>-22800</v>
       </c>
       <c r="H102" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
-        <v>222100</v>
-      </c>
       <c r="J102" s="3">
+        <v>224000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-17200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>50800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3500</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGRU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGRU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>PGRU</t>
   </si>
@@ -656,138 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>81300</v>
+        <v>27100</v>
       </c>
       <c r="E8" s="3">
-        <v>27600</v>
+        <v>30800</v>
       </c>
       <c r="F8" s="3">
-        <v>24400</v>
+        <v>29000</v>
       </c>
       <c r="G8" s="3">
-        <v>30000</v>
+        <v>27400</v>
       </c>
       <c r="H8" s="3">
-        <v>25900</v>
+        <v>24200</v>
       </c>
       <c r="I8" s="3">
+        <v>29800</v>
+      </c>
+      <c r="J8" s="3">
+        <v>25700</v>
+      </c>
+      <c r="K8" s="3">
         <v>24700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>21100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>74800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>31800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>14800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>60700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>26300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -836,8 +849,14 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -886,8 +905,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +931,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +983,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,108 +1039,126 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>4500</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>6400</v>
+        <v>-500</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G14" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>91900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>6100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>1900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>2300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>13300</v>
+        <v>4800</v>
       </c>
       <c r="E15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G15" s="3">
         <v>4300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>4400</v>
       </c>
-      <c r="G15" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3700</v>
-      </c>
       <c r="I15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K15" s="3">
         <v>4400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>10400</v>
       </c>
       <c r="L15" s="3">
         <v>3700</v>
       </c>
       <c r="M15" s="3">
+        <v>10400</v>
+      </c>
+      <c r="N15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O15" s="3">
         <v>1800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>7100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>3500</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1174,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>94300</v>
+        <v>32000</v>
       </c>
       <c r="E17" s="3">
+        <v>28300</v>
+      </c>
+      <c r="F17" s="3">
+        <v>29800</v>
+      </c>
+      <c r="G17" s="3">
+        <v>34100</v>
+      </c>
+      <c r="H17" s="3">
+        <v>29400</v>
+      </c>
+      <c r="I17" s="3">
         <v>34300</v>
       </c>
-      <c r="F17" s="3">
-        <v>29600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>31900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>28100</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>27900</v>
+      </c>
+      <c r="K17" s="3">
         <v>28500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>118700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>110600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>43200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>19600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>69700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>27800</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-13000</v>
+        <v>-4900</v>
       </c>
       <c r="E18" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G18" s="3">
         <v>-6700</v>
       </c>
-      <c r="F18" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1900</v>
-      </c>
       <c r="H18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-2200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-97600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-35900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-11400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-9100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1500</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,108 +1308,122 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>800</v>
+      </c>
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-2400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>6700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>7500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-103500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-100100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-3100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>1400</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>-300</v>
+        <v>8000</v>
       </c>
       <c r="F21" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K21" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-107800</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="P21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
-        <v>500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>7300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-86400</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-129000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-107800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1393,108 +1472,126 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-11900</v>
+        <v>-4400</v>
       </c>
       <c r="E23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F23" s="3">
+        <v>400</v>
+      </c>
+      <c r="G23" s="3">
         <v>-4600</v>
       </c>
-      <c r="F23" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-3500</v>
       </c>
-      <c r="H23" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="K23" s="3">
         <v>2800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-90000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-139400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-111500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-7900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-10200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
-        <v>200</v>
+        <v>2600</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>200</v>
+      </c>
+      <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>100</v>
-      </c>
-      <c r="N24" s="3">
-        <v>400</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>100</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1640,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-12300</v>
+        <v>-4700</v>
       </c>
       <c r="E26" s="3">
+        <v>800</v>
+      </c>
+      <c r="F26" s="3">
+        <v>200</v>
+      </c>
+      <c r="G26" s="3">
         <v>-4800</v>
       </c>
-      <c r="F26" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="I26" s="3">
         <v>-3900</v>
       </c>
-      <c r="H26" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K26" s="3">
         <v>2900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-90100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-139100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-111700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-8000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-10600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1700</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-12300</v>
+        <v>-4700</v>
       </c>
       <c r="E27" s="3">
+        <v>800</v>
+      </c>
+      <c r="F27" s="3">
+        <v>200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-4800</v>
       </c>
-      <c r="F27" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="I27" s="3">
         <v>-3900</v>
       </c>
-      <c r="H27" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K27" s="3">
         <v>2900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-90100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-139100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-111700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-8000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-10600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1808,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1864,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1920,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1976,126 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>2400</v>
       </c>
-      <c r="G32" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-6700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-7500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>103500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>100100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>3100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-12300</v>
+        <v>-4700</v>
       </c>
       <c r="E33" s="3">
+        <v>800</v>
+      </c>
+      <c r="F33" s="3">
+        <v>200</v>
+      </c>
+      <c r="G33" s="3">
         <v>-4800</v>
       </c>
-      <c r="F33" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="I33" s="3">
         <v>-3900</v>
       </c>
-      <c r="H33" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K33" s="3">
         <v>2900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-90100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-139100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-111700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-8000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-10600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2144,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-12300</v>
+        <v>-4700</v>
       </c>
       <c r="E35" s="3">
+        <v>800</v>
+      </c>
+      <c r="F35" s="3">
+        <v>200</v>
+      </c>
+      <c r="G35" s="3">
         <v>-4800</v>
       </c>
-      <c r="F35" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="I35" s="3">
         <v>-3900</v>
       </c>
-      <c r="H35" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K35" s="3">
         <v>2900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-90100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-139100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-111700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-8000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-10600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2287,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,44 +2309,46 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>237000</v>
+        <v>227500</v>
       </c>
       <c r="E41" s="3">
-        <v>225900</v>
+        <v>235100</v>
       </c>
       <c r="F41" s="3">
-        <v>220400</v>
+        <v>224100</v>
       </c>
       <c r="G41" s="3">
-        <v>231500</v>
+        <v>218600</v>
       </c>
       <c r="H41" s="3">
-        <v>254300</v>
+        <v>229600</v>
       </c>
       <c r="I41" s="3">
+        <v>252200</v>
+      </c>
+      <c r="J41" s="3">
+        <v>273800</v>
+      </c>
+      <c r="K41" s="3">
         <v>276100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>276600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>52100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>57800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2188,8 +2361,14 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,8 +2417,14 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2279,17 +2464,23 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2338,8 +2529,14 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2388,44 +2585,50 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>249800</v>
+        <v>239200</v>
       </c>
       <c r="E46" s="3">
-        <v>238900</v>
+        <v>247800</v>
       </c>
       <c r="F46" s="3">
-        <v>233800</v>
+        <v>237000</v>
       </c>
       <c r="G46" s="3">
-        <v>245100</v>
+        <v>231900</v>
       </c>
       <c r="H46" s="3">
-        <v>266800</v>
+        <v>243100</v>
       </c>
       <c r="I46" s="3">
+        <v>264600</v>
+      </c>
+      <c r="J46" s="3">
+        <v>287900</v>
+      </c>
+      <c r="K46" s="3">
         <v>290300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>288300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>65200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>67300</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2438,44 +2641,50 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2500</v>
       </c>
-      <c r="E47" s="3">
-        <v>3100</v>
-      </c>
       <c r="F47" s="3">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="G47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H47" s="3">
         <v>3400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2500</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2600</v>
       </c>
       <c r="J47" s="3">
         <v>2600</v>
       </c>
       <c r="K47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="L47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M47" s="3">
         <v>1200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,44 +2697,50 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>8700</v>
+        <v>7500</v>
       </c>
       <c r="E48" s="3">
-        <v>8200</v>
+        <v>8600</v>
       </c>
       <c r="F48" s="3">
-        <v>9400</v>
+        <v>8100</v>
       </c>
       <c r="G48" s="3">
-        <v>10500</v>
+        <v>9300</v>
       </c>
       <c r="H48" s="3">
-        <v>11100</v>
+        <v>10400</v>
       </c>
       <c r="I48" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J48" s="3">
+        <v>11700</v>
+      </c>
+      <c r="K48" s="3">
         <v>11800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>12900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>13900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>13900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2538,44 +2753,50 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>286400</v>
+        <v>280800</v>
       </c>
       <c r="E49" s="3">
-        <v>285500</v>
+        <v>284000</v>
       </c>
       <c r="F49" s="3">
-        <v>293700</v>
+        <v>283200</v>
       </c>
       <c r="G49" s="3">
-        <v>294700</v>
+        <v>291300</v>
       </c>
       <c r="H49" s="3">
-        <v>298600</v>
+        <v>292300</v>
       </c>
       <c r="I49" s="3">
+        <v>296100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>295000</v>
+      </c>
+      <c r="K49" s="3">
         <v>297400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>300500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>297800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>108200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,8 +2809,14 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2865,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2921,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2738,8 +2977,14 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,44 +3033,50 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>547400</v>
+        <v>529500</v>
       </c>
       <c r="E54" s="3">
-        <v>535700</v>
+        <v>542900</v>
       </c>
       <c r="F54" s="3">
-        <v>540500</v>
+        <v>531300</v>
       </c>
       <c r="G54" s="3">
-        <v>553700</v>
+        <v>536100</v>
       </c>
       <c r="H54" s="3">
-        <v>579100</v>
+        <v>549100</v>
       </c>
       <c r="I54" s="3">
+        <v>574300</v>
+      </c>
+      <c r="J54" s="3">
+        <v>597200</v>
+      </c>
+      <c r="K54" s="3">
         <v>602200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>604300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>378100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>190400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2838,8 +3089,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +3115,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,44 +3137,46 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F57" s="3">
+        <v>20100</v>
+      </c>
+      <c r="G57" s="3">
+        <v>17700</v>
+      </c>
+      <c r="H57" s="3">
         <v>22100</v>
       </c>
-      <c r="E57" s="3">
-        <v>20200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>17800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>22300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>18800</v>
-      </c>
       <c r="I57" s="3">
+        <v>18700</v>
+      </c>
+      <c r="J57" s="3">
+        <v>32000</v>
+      </c>
+      <c r="K57" s="3">
         <v>32300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>36200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>24400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>14800</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2928,44 +3189,50 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E58" s="3">
         <v>3500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>3100</v>
       </c>
       <c r="G58" s="3">
         <v>3100</v>
       </c>
       <c r="H58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I58" s="3">
         <v>3100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="K58" s="3">
         <v>16900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>16200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2800</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,44 +3245,50 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>52100</v>
+        <v>48400</v>
       </c>
       <c r="E59" s="3">
+        <v>51700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>43700</v>
+      </c>
+      <c r="G59" s="3">
+        <v>41700</v>
+      </c>
+      <c r="H59" s="3">
+        <v>41100</v>
+      </c>
+      <c r="I59" s="3">
+        <v>47900</v>
+      </c>
+      <c r="J59" s="3">
         <v>44100</v>
       </c>
-      <c r="F59" s="3">
-        <v>42100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>41400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>48300</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>44400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>49500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>38500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>276600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3028,44 +3301,50 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>77700</v>
+        <v>71300</v>
       </c>
       <c r="E60" s="3">
-        <v>67100</v>
+        <v>77000</v>
       </c>
       <c r="F60" s="3">
-        <v>63000</v>
+        <v>66600</v>
       </c>
       <c r="G60" s="3">
-        <v>66800</v>
+        <v>62500</v>
       </c>
       <c r="H60" s="3">
-        <v>70300</v>
+        <v>66200</v>
       </c>
       <c r="I60" s="3">
+        <v>69700</v>
+      </c>
+      <c r="J60" s="3">
+        <v>92800</v>
+      </c>
+      <c r="K60" s="3">
         <v>93600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>101900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>66400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>294200</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3078,44 +3357,50 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4700</v>
       </c>
-      <c r="E61" s="3">
-        <v>4900</v>
-      </c>
       <c r="F61" s="3">
+        <v>4800</v>
+      </c>
+      <c r="G61" s="3">
         <v>5500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6200</v>
       </c>
-      <c r="H61" s="3">
-        <v>7000</v>
-      </c>
       <c r="I61" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J61" s="3">
         <v>7700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
+        <v>7700</v>
+      </c>
+      <c r="L61" s="3">
         <v>8700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>21700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>22300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3128,44 +3413,50 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E62" s="3">
         <v>3300</v>
       </c>
-      <c r="E62" s="3">
-        <v>5700</v>
-      </c>
       <c r="F62" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G62" s="3">
         <v>7200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2700</v>
       </c>
       <c r="K62" s="3">
         <v>2600</v>
       </c>
       <c r="L62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N62" s="3">
         <v>1600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3178,8 +3469,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3525,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3581,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,44 +3637,50 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>85700</v>
+        <v>80500</v>
       </c>
       <c r="E66" s="3">
-        <v>77700</v>
+        <v>85000</v>
       </c>
       <c r="F66" s="3">
-        <v>75700</v>
+        <v>77000</v>
       </c>
       <c r="G66" s="3">
-        <v>78800</v>
+        <v>75100</v>
       </c>
       <c r="H66" s="3">
-        <v>79300</v>
+        <v>78200</v>
       </c>
       <c r="I66" s="3">
+        <v>78700</v>
+      </c>
+      <c r="J66" s="3">
+        <v>103100</v>
+      </c>
+      <c r="K66" s="3">
         <v>103900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>113200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>90700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>318100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3693,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3719,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3771,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3827,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3528,14 +3863,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>44000</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3548,8 +3883,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,44 +3939,50 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-336300</v>
+        <v>-335500</v>
       </c>
       <c r="E72" s="3">
-        <v>-336800</v>
+        <v>-333600</v>
       </c>
       <c r="F72" s="3">
-        <v>-328400</v>
+        <v>-334000</v>
       </c>
       <c r="G72" s="3">
-        <v>-322000</v>
+        <v>-325700</v>
       </c>
       <c r="H72" s="3">
-        <v>-317900</v>
+        <v>-319300</v>
       </c>
       <c r="I72" s="3">
+        <v>-315300</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-310500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-313100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-316300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-222600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-200300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,8 +3995,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +4051,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +4107,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,44 +4163,50 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>461700</v>
+        <v>449100</v>
       </c>
       <c r="E76" s="3">
-        <v>458100</v>
+        <v>457900</v>
       </c>
       <c r="F76" s="3">
-        <v>464800</v>
+        <v>454300</v>
       </c>
       <c r="G76" s="3">
-        <v>474900</v>
+        <v>461000</v>
       </c>
       <c r="H76" s="3">
-        <v>499800</v>
+        <v>471000</v>
       </c>
       <c r="I76" s="3">
+        <v>495600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>494200</v>
+      </c>
+      <c r="K76" s="3">
         <v>498300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>491100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>287400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-171800</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3848,8 +4219,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4275,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-12300</v>
+        <v>-4700</v>
       </c>
       <c r="E81" s="3">
+        <v>800</v>
+      </c>
+      <c r="F81" s="3">
+        <v>200</v>
+      </c>
+      <c r="G81" s="3">
         <v>-4800</v>
       </c>
-      <c r="F81" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="I81" s="3">
         <v>-3900</v>
       </c>
-      <c r="H81" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K81" s="3">
         <v>2900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-90100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-139100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-111700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-8000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-10600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,58 +4418,66 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>13300</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E83" s="3">
-        <v>4300</v>
+        <v>4600</v>
       </c>
       <c r="F83" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G83" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H83" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="I83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K83" s="3">
         <v>4400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>10400</v>
       </c>
       <c r="L83" s="3">
         <v>3700</v>
       </c>
       <c r="M83" s="3">
+        <v>10400</v>
+      </c>
+      <c r="N83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O83" s="3">
         <v>1800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>7100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4526,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4582,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4638,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4694,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4750,70 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>20400</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E89" s="3">
-        <v>8200</v>
+        <v>3800</v>
       </c>
       <c r="F89" s="3">
-        <v>-3700</v>
+        <v>15700</v>
       </c>
       <c r="G89" s="3">
-        <v>-12500</v>
+        <v>4500</v>
       </c>
       <c r="H89" s="3">
-        <v>-4400</v>
+        <v>13200</v>
       </c>
       <c r="I89" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="K89" s="3">
         <v>5400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-5500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-5000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,58 +4832,66 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9900</v>
       </c>
-      <c r="J91" s="3">
-        <v>-200</v>
-      </c>
       <c r="K91" s="3">
-        <v>-1200</v>
+        <v>-9900</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4940,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4996,70 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-15300</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
-        <v>-5100</v>
+        <v>-4200</v>
       </c>
       <c r="F94" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="H94" s="3">
+        <v>14200</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="J94" s="3">
         <v>-5000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-6800</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-3200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-8000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-4000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-16600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-13500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +5078,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4663,8 +5130,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +5186,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5242,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,90 +5298,102 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-2400</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
-        <v>-1000</v>
+        <v>-800</v>
       </c>
       <c r="F100" s="3">
         <v>-700</v>
       </c>
       <c r="G100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>232700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-7400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>65400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>18800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>2900</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E101" s="3">
-        <v>3400</v>
+        <v>-6400</v>
       </c>
       <c r="F101" s="3">
-        <v>-1800</v>
+        <v>1200</v>
       </c>
       <c r="G101" s="3">
-        <v>-10600</v>
+        <v>1700</v>
       </c>
       <c r="H101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="J101" s="3">
         <v>3900</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4913,54 +5410,66 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>5500</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E102" s="3">
-        <v>5500</v>
+        <v>-7600</v>
       </c>
       <c r="F102" s="3">
-        <v>-11100</v>
+        <v>11000</v>
       </c>
       <c r="G102" s="3">
-        <v>-22800</v>
+        <v>-5500</v>
       </c>
       <c r="H102" s="3">
-        <v>-21800</v>
+        <v>-188500</v>
       </c>
       <c r="I102" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>224000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-17200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-11500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-6900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>50800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>3500</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGRU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGRU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>PGRU</t>
   </si>
@@ -749,25 +749,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>27100</v>
+        <v>28100</v>
       </c>
       <c r="E8" s="3">
-        <v>30800</v>
+        <v>32000</v>
       </c>
       <c r="F8" s="3">
-        <v>29000</v>
+        <v>30100</v>
       </c>
       <c r="G8" s="3">
-        <v>27400</v>
+        <v>28400</v>
       </c>
       <c r="H8" s="3">
-        <v>24200</v>
+        <v>25100</v>
       </c>
       <c r="I8" s="3">
-        <v>29800</v>
+        <v>30900</v>
       </c>
       <c r="J8" s="3">
-        <v>25700</v>
+        <v>26700</v>
       </c>
       <c r="K8" s="3">
         <v>24700</v>
@@ -1057,10 +1057,10 @@
         <v>-500</v>
       </c>
       <c r="F14" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="G14" s="3">
-        <v>6300</v>
+        <v>6600</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1107,25 +1107,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4800</v>
       </c>
-      <c r="E15" s="3">
-        <v>4600</v>
-      </c>
       <c r="F15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G15" s="3">
         <v>4500</v>
       </c>
-      <c r="G15" s="3">
-        <v>4300</v>
-      </c>
       <c r="H15" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="I15" s="3">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="J15" s="3">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="K15" s="3">
         <v>4400</v>
@@ -1182,25 +1182,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>32000</v>
+        <v>33200</v>
       </c>
       <c r="E17" s="3">
-        <v>28300</v>
+        <v>29300</v>
       </c>
       <c r="F17" s="3">
-        <v>29800</v>
+        <v>30900</v>
       </c>
       <c r="G17" s="3">
-        <v>34100</v>
+        <v>35400</v>
       </c>
       <c r="H17" s="3">
-        <v>29400</v>
+        <v>30500</v>
       </c>
       <c r="I17" s="3">
-        <v>34300</v>
+        <v>35600</v>
       </c>
       <c r="J17" s="3">
-        <v>27900</v>
+        <v>28900</v>
       </c>
       <c r="K17" s="3">
         <v>28500</v>
@@ -1238,22 +1238,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4900</v>
+        <v>-5100</v>
       </c>
       <c r="E18" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="F18" s="3">
         <v>-700</v>
       </c>
       <c r="G18" s="3">
-        <v>-6700</v>
+        <v>-6900</v>
       </c>
       <c r="H18" s="3">
-        <v>-5100</v>
+        <v>-5300</v>
       </c>
       <c r="I18" s="3">
-        <v>-4600</v>
+        <v>-4700</v>
       </c>
       <c r="J18" s="3">
         <v>-2200</v>
@@ -1316,7 +1316,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E20" s="3">
         <v>800</v>
@@ -1328,13 +1328,13 @@
         <v>2100</v>
       </c>
       <c r="H20" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="I20" s="3">
         <v>1100</v>
       </c>
       <c r="J20" s="3">
-        <v>-3000</v>
+        <v>-3100</v>
       </c>
       <c r="K20" s="3">
         <v>6700</v>
@@ -1371,23 +1371,23 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>400</v>
       </c>
       <c r="E21" s="3">
-        <v>8000</v>
+        <v>8300</v>
       </c>
       <c r="F21" s="3">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="G21" s="3">
-        <v>4000</v>
+        <v>-300</v>
       </c>
       <c r="H21" s="3">
-        <v>-18900</v>
+        <v>-3300</v>
       </c>
       <c r="I21" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J21" s="3">
         <v>-1500</v>
@@ -1484,25 +1484,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-4400</v>
+        <v>-4600</v>
       </c>
       <c r="E23" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="F23" s="3">
         <v>400</v>
       </c>
       <c r="G23" s="3">
-        <v>-4600</v>
+        <v>-4800</v>
       </c>
       <c r="H23" s="3">
-        <v>-7500</v>
+        <v>-7800</v>
       </c>
       <c r="I23" s="3">
-        <v>-3500</v>
+        <v>-3600</v>
       </c>
       <c r="J23" s="3">
-        <v>-5100</v>
+        <v>-5300</v>
       </c>
       <c r="K23" s="3">
         <v>2800</v>
@@ -1652,7 +1652,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="E26" s="3">
         <v>800</v>
@@ -1661,16 +1661,16 @@
         <v>200</v>
       </c>
       <c r="G26" s="3">
-        <v>-4800</v>
+        <v>-5000</v>
       </c>
       <c r="H26" s="3">
-        <v>-7600</v>
+        <v>-7900</v>
       </c>
       <c r="I26" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="J26" s="3">
-        <v>-5500</v>
+        <v>-5700</v>
       </c>
       <c r="K26" s="3">
         <v>2900</v>
@@ -1708,7 +1708,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="E27" s="3">
         <v>800</v>
@@ -1717,16 +1717,16 @@
         <v>200</v>
       </c>
       <c r="G27" s="3">
-        <v>-4800</v>
+        <v>-5000</v>
       </c>
       <c r="H27" s="3">
-        <v>-7600</v>
+        <v>-7900</v>
       </c>
       <c r="I27" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="J27" s="3">
-        <v>-5500</v>
+        <v>-5700</v>
       </c>
       <c r="K27" s="3">
         <v>2900</v>
@@ -1988,7 +1988,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="E32" s="3">
         <v>-800</v>
@@ -2000,13 +2000,13 @@
         <v>-2100</v>
       </c>
       <c r="H32" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="I32" s="3">
         <v>-1100</v>
       </c>
       <c r="J32" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="K32" s="3">
         <v>-6700</v>
@@ -2044,7 +2044,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="E33" s="3">
         <v>800</v>
@@ -2053,16 +2053,16 @@
         <v>200</v>
       </c>
       <c r="G33" s="3">
-        <v>-4800</v>
+        <v>-5000</v>
       </c>
       <c r="H33" s="3">
-        <v>-7600</v>
+        <v>-7900</v>
       </c>
       <c r="I33" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="J33" s="3">
-        <v>-5500</v>
+        <v>-5700</v>
       </c>
       <c r="K33" s="3">
         <v>2900</v>
@@ -2156,7 +2156,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="E35" s="3">
         <v>800</v>
@@ -2165,16 +2165,16 @@
         <v>200</v>
       </c>
       <c r="G35" s="3">
-        <v>-4800</v>
+        <v>-5000</v>
       </c>
       <c r="H35" s="3">
-        <v>-7600</v>
+        <v>-7900</v>
       </c>
       <c r="I35" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="J35" s="3">
-        <v>-5500</v>
+        <v>-5700</v>
       </c>
       <c r="K35" s="3">
         <v>2900</v>
@@ -2317,25 +2317,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>227500</v>
+        <v>231500</v>
       </c>
       <c r="E41" s="3">
-        <v>235100</v>
+        <v>236100</v>
       </c>
       <c r="F41" s="3">
-        <v>224100</v>
+        <v>244000</v>
       </c>
       <c r="G41" s="3">
-        <v>218600</v>
+        <v>232600</v>
       </c>
       <c r="H41" s="3">
-        <v>229600</v>
+        <v>226900</v>
       </c>
       <c r="I41" s="3">
-        <v>252200</v>
+        <v>238300</v>
       </c>
       <c r="J41" s="3">
-        <v>273800</v>
+        <v>261800</v>
       </c>
       <c r="K41" s="3">
         <v>276100</v>
@@ -2597,25 +2597,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>239200</v>
+        <v>243600</v>
       </c>
       <c r="E46" s="3">
-        <v>247800</v>
+        <v>248300</v>
       </c>
       <c r="F46" s="3">
-        <v>237000</v>
+        <v>257200</v>
       </c>
       <c r="G46" s="3">
-        <v>231900</v>
+        <v>246000</v>
       </c>
       <c r="H46" s="3">
-        <v>243100</v>
+        <v>240700</v>
       </c>
       <c r="I46" s="3">
-        <v>264600</v>
+        <v>252300</v>
       </c>
       <c r="J46" s="3">
-        <v>287900</v>
+        <v>274700</v>
       </c>
       <c r="K46" s="3">
         <v>290300</v>
@@ -2653,22 +2653,22 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2000</v>
+        <v>1700</v>
       </c>
       <c r="E47" s="3">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="F47" s="3">
-        <v>3000</v>
+        <v>2600</v>
       </c>
       <c r="G47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H47" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I47" s="3">
         <v>3500</v>
-      </c>
-      <c r="H47" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2500</v>
       </c>
       <c r="J47" s="3">
         <v>2600</v>
@@ -2709,25 +2709,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7500</v>
+        <v>6900</v>
       </c>
       <c r="E48" s="3">
-        <v>8600</v>
+        <v>7800</v>
       </c>
       <c r="F48" s="3">
-        <v>8100</v>
+        <v>8900</v>
       </c>
       <c r="G48" s="3">
-        <v>9300</v>
+        <v>8400</v>
       </c>
       <c r="H48" s="3">
-        <v>10400</v>
+        <v>9600</v>
       </c>
       <c r="I48" s="3">
-        <v>11000</v>
+        <v>10800</v>
       </c>
       <c r="J48" s="3">
-        <v>11700</v>
+        <v>11500</v>
       </c>
       <c r="K48" s="3">
         <v>11800</v>
@@ -2765,25 +2765,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>280800</v>
+        <v>291200</v>
       </c>
       <c r="E49" s="3">
-        <v>284000</v>
+        <v>291500</v>
       </c>
       <c r="F49" s="3">
-        <v>283200</v>
+        <v>294800</v>
       </c>
       <c r="G49" s="3">
-        <v>291300</v>
+        <v>293900</v>
       </c>
       <c r="H49" s="3">
-        <v>292300</v>
+        <v>302400</v>
       </c>
       <c r="I49" s="3">
-        <v>296100</v>
+        <v>303400</v>
       </c>
       <c r="J49" s="3">
-        <v>295000</v>
+        <v>307400</v>
       </c>
       <c r="K49" s="3">
         <v>297400</v>
@@ -3045,25 +3045,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>529500</v>
+        <v>543400</v>
       </c>
       <c r="E54" s="3">
-        <v>542900</v>
+        <v>549600</v>
       </c>
       <c r="F54" s="3">
-        <v>531300</v>
+        <v>563500</v>
       </c>
       <c r="G54" s="3">
-        <v>536100</v>
+        <v>551500</v>
       </c>
       <c r="H54" s="3">
-        <v>549100</v>
+        <v>556400</v>
       </c>
       <c r="I54" s="3">
-        <v>574300</v>
+        <v>570000</v>
       </c>
       <c r="J54" s="3">
-        <v>597200</v>
+        <v>596100</v>
       </c>
       <c r="K54" s="3">
         <v>602200</v>
@@ -3145,25 +3145,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>19800</v>
+        <v>19000</v>
       </c>
       <c r="E57" s="3">
-        <v>21900</v>
+        <v>20500</v>
       </c>
       <c r="F57" s="3">
-        <v>20100</v>
+        <v>22700</v>
       </c>
       <c r="G57" s="3">
-        <v>17700</v>
+        <v>20800</v>
       </c>
       <c r="H57" s="3">
-        <v>22100</v>
+        <v>18300</v>
       </c>
       <c r="I57" s="3">
-        <v>18700</v>
+        <v>22900</v>
       </c>
       <c r="J57" s="3">
-        <v>32000</v>
+        <v>19400</v>
       </c>
       <c r="K57" s="3">
         <v>32300</v>
@@ -3201,25 +3201,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="E58" s="3">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="F58" s="3">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="G58" s="3">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="H58" s="3">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="I58" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="J58" s="3">
-        <v>16700</v>
+        <v>3200</v>
       </c>
       <c r="K58" s="3">
         <v>16900</v>
@@ -3257,25 +3257,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>48400</v>
+        <v>48000</v>
       </c>
       <c r="E59" s="3">
-        <v>51700</v>
+        <v>50300</v>
       </c>
       <c r="F59" s="3">
-        <v>43700</v>
+        <v>53600</v>
       </c>
       <c r="G59" s="3">
-        <v>41700</v>
+        <v>45300</v>
       </c>
       <c r="H59" s="3">
-        <v>41100</v>
+        <v>43300</v>
       </c>
       <c r="I59" s="3">
-        <v>47900</v>
+        <v>42600</v>
       </c>
       <c r="J59" s="3">
-        <v>44100</v>
+        <v>49700</v>
       </c>
       <c r="K59" s="3">
         <v>44400</v>
@@ -3313,25 +3313,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>71300</v>
+        <v>70000</v>
       </c>
       <c r="E60" s="3">
-        <v>77000</v>
+        <v>74100</v>
       </c>
       <c r="F60" s="3">
-        <v>66600</v>
+        <v>80000</v>
       </c>
       <c r="G60" s="3">
-        <v>62500</v>
+        <v>69100</v>
       </c>
       <c r="H60" s="3">
-        <v>66200</v>
+        <v>64800</v>
       </c>
       <c r="I60" s="3">
-        <v>69700</v>
+        <v>68700</v>
       </c>
       <c r="J60" s="3">
-        <v>92800</v>
+        <v>72300</v>
       </c>
       <c r="K60" s="3">
         <v>93600</v>
@@ -3369,25 +3369,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E61" s="3">
-        <v>4700</v>
+        <v>4100</v>
       </c>
       <c r="F61" s="3">
         <v>4800</v>
       </c>
       <c r="G61" s="3">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="H61" s="3">
-        <v>6200</v>
+        <v>5700</v>
       </c>
       <c r="I61" s="3">
-        <v>6900</v>
+        <v>6400</v>
       </c>
       <c r="J61" s="3">
-        <v>7700</v>
+        <v>7200</v>
       </c>
       <c r="K61" s="3">
         <v>7700</v>
@@ -3425,25 +3425,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5100</v>
+        <v>5600</v>
       </c>
       <c r="E62" s="3">
-        <v>3300</v>
+        <v>5300</v>
       </c>
       <c r="F62" s="3">
-        <v>5600</v>
+        <v>3400</v>
       </c>
       <c r="G62" s="3">
-        <v>7200</v>
+        <v>5800</v>
       </c>
       <c r="H62" s="3">
-        <v>5800</v>
+        <v>7400</v>
       </c>
       <c r="I62" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J62" s="3">
         <v>2100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2600</v>
       </c>
       <c r="K62" s="3">
         <v>2600</v>
@@ -3649,25 +3649,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>80500</v>
+        <v>79100</v>
       </c>
       <c r="E66" s="3">
-        <v>85000</v>
+        <v>83500</v>
       </c>
       <c r="F66" s="3">
-        <v>77000</v>
+        <v>88200</v>
       </c>
       <c r="G66" s="3">
-        <v>75100</v>
+        <v>80000</v>
       </c>
       <c r="H66" s="3">
-        <v>78200</v>
+        <v>77900</v>
       </c>
       <c r="I66" s="3">
-        <v>78700</v>
+        <v>81200</v>
       </c>
       <c r="J66" s="3">
-        <v>103100</v>
+        <v>81600</v>
       </c>
       <c r="K66" s="3">
         <v>103900</v>
@@ -3951,25 +3951,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-335500</v>
+        <v>-352300</v>
       </c>
       <c r="E72" s="3">
-        <v>-333600</v>
+        <v>-348200</v>
       </c>
       <c r="F72" s="3">
-        <v>-334000</v>
+        <v>-346200</v>
       </c>
       <c r="G72" s="3">
-        <v>-325700</v>
+        <v>-346700</v>
       </c>
       <c r="H72" s="3">
-        <v>-319300</v>
+        <v>-338100</v>
       </c>
       <c r="I72" s="3">
-        <v>-315300</v>
+        <v>-331500</v>
       </c>
       <c r="J72" s="3">
-        <v>-310500</v>
+        <v>-327300</v>
       </c>
       <c r="K72" s="3">
         <v>-313100</v>
@@ -4175,25 +4175,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>449100</v>
+        <v>464400</v>
       </c>
       <c r="E76" s="3">
-        <v>457900</v>
+        <v>466100</v>
       </c>
       <c r="F76" s="3">
-        <v>454300</v>
+        <v>475300</v>
       </c>
       <c r="G76" s="3">
-        <v>461000</v>
+        <v>471600</v>
       </c>
       <c r="H76" s="3">
-        <v>471000</v>
+        <v>478500</v>
       </c>
       <c r="I76" s="3">
-        <v>495600</v>
+        <v>488900</v>
       </c>
       <c r="J76" s="3">
-        <v>494200</v>
+        <v>514500</v>
       </c>
       <c r="K76" s="3">
         <v>498300</v>
@@ -4348,7 +4348,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="E81" s="3">
         <v>800</v>
@@ -4357,16 +4357,16 @@
         <v>200</v>
       </c>
       <c r="G81" s="3">
-        <v>-4800</v>
+        <v>-5000</v>
       </c>
       <c r="H81" s="3">
-        <v>-7600</v>
+        <v>-7900</v>
       </c>
       <c r="I81" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="J81" s="3">
-        <v>-5500</v>
+        <v>-5700</v>
       </c>
       <c r="K81" s="3">
         <v>2900</v>
@@ -4425,26 +4425,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>5000</v>
       </c>
       <c r="E83" s="3">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="F83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G83" s="3">
         <v>4500</v>
       </c>
-      <c r="G83" s="3">
-        <v>8600</v>
-      </c>
       <c r="H83" s="3">
-        <v>-11400</v>
+        <v>4500</v>
       </c>
       <c r="I83" s="3">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="J83" s="3">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="K83" s="3">
         <v>4400</v>
@@ -4761,26 +4761,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-1900</v>
       </c>
       <c r="E89" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="F89" s="3">
-        <v>15700</v>
+        <v>16300</v>
       </c>
       <c r="G89" s="3">
-        <v>4500</v>
+        <v>8400</v>
       </c>
       <c r="H89" s="3">
-        <v>13200</v>
+        <v>-3800</v>
       </c>
       <c r="I89" s="3">
-        <v>-12400</v>
+        <v>-12800</v>
       </c>
       <c r="J89" s="3">
-        <v>-4300</v>
+        <v>-4500</v>
       </c>
       <c r="K89" s="3">
         <v>5400</v>
@@ -4843,22 +4843,22 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-12900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8800</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-9900</v>
       </c>
       <c r="K91" s="3">
         <v>-9900</v>
@@ -5007,26 +5007,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-5500</v>
       </c>
       <c r="E94" s="3">
-        <v>-4200</v>
+        <v>-4300</v>
       </c>
       <c r="F94" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="G94" s="3">
         <v>-5200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-10000</v>
-      </c>
       <c r="H94" s="3">
-        <v>14200</v>
+        <v>-5100</v>
       </c>
       <c r="I94" s="3">
-        <v>-6800</v>
+        <v>-7000</v>
       </c>
       <c r="J94" s="3">
-        <v>-5000</v>
+        <v>-5200</v>
       </c>
       <c r="K94" s="3">
         <v>-4300</v>
@@ -5309,26 +5309,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>-1000</v>
       </c>
       <c r="E100" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="F100" s="3">
         <v>-700</v>
       </c>
       <c r="G100" s="3">
-        <v>-1700</v>
+        <v>-1000</v>
       </c>
       <c r="H100" s="3">
-        <v>-217000</v>
+        <v>-700</v>
       </c>
       <c r="I100" s="3">
         <v>-600</v>
       </c>
       <c r="J100" s="3">
-        <v>-14100</v>
+        <v>-14700</v>
       </c>
       <c r="K100" s="3">
         <v>200</v>
@@ -5365,26 +5365,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>3800</v>
       </c>
       <c r="E101" s="3">
-        <v>-6400</v>
+        <v>-6600</v>
       </c>
       <c r="F101" s="3">
         <v>1200</v>
       </c>
       <c r="G101" s="3">
-        <v>1700</v>
+        <v>3500</v>
       </c>
       <c r="H101" s="3">
-        <v>1100</v>
+        <v>-1800</v>
       </c>
       <c r="I101" s="3">
-        <v>-10500</v>
+        <v>-10900</v>
       </c>
       <c r="J101" s="3">
-        <v>3900</v>
+        <v>4100</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -5421,26 +5421,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-4600</v>
       </c>
       <c r="E102" s="3">
-        <v>-7600</v>
+        <v>-7800</v>
       </c>
       <c r="F102" s="3">
-        <v>11000</v>
+        <v>11400</v>
       </c>
       <c r="G102" s="3">
-        <v>-5500</v>
+        <v>5700</v>
       </c>
       <c r="H102" s="3">
-        <v>-188500</v>
+        <v>-11400</v>
       </c>
       <c r="I102" s="3">
-        <v>-22600</v>
+        <v>-23400</v>
       </c>
       <c r="J102" s="3">
-        <v>-21600</v>
+        <v>-22500</v>
       </c>
       <c r="K102" s="3">
         <v>-500</v>

--- a/AAII_Financials/Quarterly/PGRU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGRU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
   <si>
     <t>PGRU</t>
   </si>
@@ -656,174 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>28100</v>
+        <v>30000</v>
       </c>
       <c r="E8" s="3">
-        <v>32000</v>
+        <v>27100</v>
       </c>
       <c r="F8" s="3">
-        <v>30100</v>
+        <v>31400</v>
       </c>
       <c r="G8" s="3">
-        <v>28400</v>
+        <v>28600</v>
       </c>
       <c r="H8" s="3">
-        <v>25100</v>
+        <v>27300</v>
       </c>
       <c r="I8" s="3">
-        <v>30900</v>
+        <v>24500</v>
       </c>
       <c r="J8" s="3">
+        <v>29900</v>
+      </c>
+      <c r="K8" s="3">
         <v>26700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>74800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>31800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>60700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>26300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>11300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>13100</v>
+      </c>
+      <c r="H9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>16100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>12200</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -855,31 +862,34 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>20100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>15500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>12200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>8500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>17700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -911,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,22 +946,23 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
+      <c r="E12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2500</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -956,8 +970,8 @@
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="J12" s="3">
+        <v>17700</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,69 +1062,75 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="L14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M14" s="3">
+        <v>91900</v>
+      </c>
+      <c r="N14" s="3">
+        <v>6100</v>
+      </c>
+      <c r="O14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P14" s="3">
         <v>-500</v>
       </c>
-      <c r="F14" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G14" s="3">
-        <v>6600</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>900</v>
-      </c>
-      <c r="J14" s="3">
-        <v>100</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="L14" s="3">
-        <v>91900</v>
-      </c>
-      <c r="M14" s="3">
-        <v>6100</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1900</v>
-      </c>
-      <c r="O14" s="3">
-        <v>-500</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="E15" s="3">
         <v>4800</v>
@@ -1116,49 +1139,52 @@
         <v>4700</v>
       </c>
       <c r="G15" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="H15" s="3">
-        <v>4500</v>
+        <v>4300</v>
       </c>
       <c r="I15" s="3">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="J15" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K15" s="3">
         <v>3800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>10400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3500</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>33200</v>
+        <v>34300</v>
       </c>
       <c r="E17" s="3">
-        <v>29300</v>
+        <v>31900</v>
       </c>
       <c r="F17" s="3">
-        <v>30900</v>
+        <v>28700</v>
       </c>
       <c r="G17" s="3">
-        <v>35400</v>
+        <v>29600</v>
       </c>
       <c r="H17" s="3">
-        <v>30500</v>
+        <v>29200</v>
       </c>
       <c r="I17" s="3">
-        <v>35600</v>
+        <v>29800</v>
       </c>
       <c r="J17" s="3">
+        <v>32800</v>
+      </c>
+      <c r="K17" s="3">
         <v>28900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>118700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>110600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>69700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27800</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-5100</v>
+        <v>-4300</v>
       </c>
       <c r="E18" s="3">
-        <v>2700</v>
+        <v>-4800</v>
       </c>
       <c r="F18" s="3">
-        <v>-700</v>
+        <v>2800</v>
       </c>
       <c r="G18" s="3">
-        <v>-6900</v>
+        <v>-900</v>
       </c>
       <c r="H18" s="3">
-        <v>-5300</v>
+        <v>-1900</v>
       </c>
       <c r="I18" s="3">
-        <v>-4700</v>
+        <v>-5200</v>
       </c>
       <c r="J18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-97600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-35900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,140 +1343,147 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>500</v>
+        <v>6900</v>
       </c>
       <c r="E20" s="3">
-        <v>800</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
-        <v>1100</v>
+        <v>5200</v>
       </c>
       <c r="G20" s="3">
-        <v>2100</v>
+        <v>-1300</v>
       </c>
       <c r="H20" s="3">
-        <v>-2500</v>
+        <v>-1600</v>
       </c>
       <c r="I20" s="3">
-        <v>1100</v>
+        <v>2300</v>
       </c>
       <c r="J20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-103500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E21" s="3">
         <v>400</v>
       </c>
-      <c r="E21" s="3">
-        <v>8300</v>
-      </c>
       <c r="F21" s="3">
-        <v>5100</v>
+        <v>2300</v>
       </c>
       <c r="G21" s="3">
-        <v>-300</v>
+        <v>4800</v>
       </c>
       <c r="H21" s="3">
-        <v>-3300</v>
+        <v>4000</v>
       </c>
       <c r="I21" s="3">
-        <v>600</v>
+        <v>-3100</v>
       </c>
       <c r="J21" s="3">
         <v>-1500</v>
       </c>
       <c r="K21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="L21" s="3">
         <v>7300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-86400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-129000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-107800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1478,120 +1518,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G23" s="3">
+        <v>400</v>
+      </c>
+      <c r="H23" s="3">
         <v>-4600</v>
       </c>
-      <c r="E23" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F23" s="3">
-        <v>400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-7800</v>
-      </c>
       <c r="I23" s="3">
-        <v>-3600</v>
+        <v>-7600</v>
       </c>
       <c r="J23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-5300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-90000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-139400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-111500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1600</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>400</v>
       </c>
       <c r="J24" s="3">
         <v>400</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F26" s="3">
+        <v>800</v>
+      </c>
+      <c r="G26" s="3">
+        <v>200</v>
+      </c>
+      <c r="H26" s="3">
         <v>-4800</v>
       </c>
-      <c r="E26" s="3">
-        <v>800</v>
-      </c>
-      <c r="F26" s="3">
-        <v>200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-7900</v>
-      </c>
       <c r="I26" s="3">
-        <v>-4000</v>
+        <v>-7700</v>
       </c>
       <c r="J26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-90100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-139100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-111700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1700</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F27" s="3">
+        <v>800</v>
+      </c>
+      <c r="G27" s="3">
+        <v>200</v>
+      </c>
+      <c r="H27" s="3">
         <v>-4800</v>
       </c>
-      <c r="E27" s="3">
-        <v>800</v>
-      </c>
-      <c r="F27" s="3">
-        <v>200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-7900</v>
-      </c>
       <c r="I27" s="3">
-        <v>-4000</v>
+        <v>-7700</v>
       </c>
       <c r="J27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-90100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-139100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-111700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1700</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-500</v>
+        <v>-6900</v>
       </c>
       <c r="E32" s="3">
-        <v>-800</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
-        <v>-1100</v>
+        <v>-5200</v>
       </c>
       <c r="G32" s="3">
-        <v>-2100</v>
+        <v>1300</v>
       </c>
       <c r="H32" s="3">
-        <v>2500</v>
+        <v>1600</v>
       </c>
       <c r="I32" s="3">
-        <v>-1100</v>
+        <v>-2300</v>
       </c>
       <c r="J32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K32" s="3">
         <v>3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>103500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F33" s="3">
+        <v>800</v>
+      </c>
+      <c r="G33" s="3">
+        <v>200</v>
+      </c>
+      <c r="H33" s="3">
         <v>-4800</v>
       </c>
-      <c r="E33" s="3">
-        <v>800</v>
-      </c>
-      <c r="F33" s="3">
-        <v>200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-7900</v>
-      </c>
       <c r="I33" s="3">
-        <v>-4000</v>
+        <v>-7700</v>
       </c>
       <c r="J33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-90100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-139100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-111700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1700</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F35" s="3">
+        <v>800</v>
+      </c>
+      <c r="G35" s="3">
+        <v>200</v>
+      </c>
+      <c r="H35" s="3">
         <v>-4800</v>
       </c>
-      <c r="E35" s="3">
-        <v>800</v>
-      </c>
-      <c r="F35" s="3">
-        <v>200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-7900</v>
-      </c>
       <c r="I35" s="3">
-        <v>-4000</v>
+        <v>-7700</v>
       </c>
       <c r="J35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-90100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-139100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-111700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1700</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,47 +2397,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>231500</v>
+        <v>228200</v>
       </c>
       <c r="E41" s="3">
-        <v>236100</v>
+        <v>222800</v>
       </c>
       <c r="F41" s="3">
-        <v>244000</v>
+        <v>232100</v>
       </c>
       <c r="G41" s="3">
-        <v>232600</v>
+        <v>231800</v>
       </c>
       <c r="H41" s="3">
-        <v>226900</v>
+        <v>223000</v>
       </c>
       <c r="I41" s="3">
-        <v>238300</v>
+        <v>221400</v>
       </c>
       <c r="J41" s="3">
+        <v>230600</v>
+      </c>
+      <c r="K41" s="3">
         <v>261800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>276100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>276600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>57800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2454,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2379,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -2391,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2423,31 +2513,34 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>12100</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2470,8 +2563,8 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+      <c r="R43" s="3">
+        <v>0</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
@@ -2479,31 +2572,34 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2535,31 +2631,34 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2591,47 +2690,50 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>243600</v>
+        <v>240300</v>
       </c>
       <c r="E46" s="3">
-        <v>248300</v>
+        <v>234400</v>
       </c>
       <c r="F46" s="3">
-        <v>257200</v>
+        <v>244100</v>
       </c>
       <c r="G46" s="3">
-        <v>246000</v>
+        <v>244400</v>
       </c>
       <c r="H46" s="3">
-        <v>240700</v>
+        <v>235800</v>
       </c>
       <c r="I46" s="3">
-        <v>252300</v>
+        <v>234900</v>
       </c>
       <c r="J46" s="3">
+        <v>244200</v>
+      </c>
+      <c r="K46" s="3">
         <v>274700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>290300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>288300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>65200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>67300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,31 +2749,34 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G47" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H47" s="3">
-        <v>3700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J47" s="3">
-        <v>2600</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>2600</v>
@@ -2680,14 +2785,14 @@
         <v>2600</v>
       </c>
       <c r="M47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N47" s="3">
         <v>1200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2703,46 +2808,49 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6900</v>
+        <v>6100</v>
       </c>
       <c r="E48" s="3">
-        <v>7800</v>
+        <v>6600</v>
       </c>
       <c r="F48" s="3">
-        <v>8900</v>
+        <v>7700</v>
       </c>
       <c r="G48" s="3">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="H48" s="3">
-        <v>9600</v>
+        <v>8100</v>
       </c>
       <c r="I48" s="3">
-        <v>10800</v>
+        <v>9400</v>
       </c>
       <c r="J48" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K48" s="3">
         <v>11500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>13900</v>
       </c>
       <c r="N48" s="3">
         <v>13900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>13900</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
@@ -2759,47 +2867,50 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>291200</v>
+        <v>279400</v>
       </c>
       <c r="E49" s="3">
-        <v>291500</v>
+        <v>280300</v>
       </c>
       <c r="F49" s="3">
-        <v>294800</v>
+        <v>276400</v>
       </c>
       <c r="G49" s="3">
-        <v>293900</v>
+        <v>280100</v>
       </c>
       <c r="H49" s="3">
-        <v>302400</v>
+        <v>281800</v>
       </c>
       <c r="I49" s="3">
-        <v>303400</v>
+        <v>295000</v>
       </c>
       <c r="J49" s="3">
+        <v>289100</v>
+      </c>
+      <c r="K49" s="3">
         <v>307400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>297400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>300500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>297800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>108200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,31 +3044,34 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,47 +3162,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>543400</v>
+        <v>527600</v>
       </c>
       <c r="E54" s="3">
-        <v>549600</v>
+        <v>523000</v>
       </c>
       <c r="F54" s="3">
-        <v>563500</v>
+        <v>540300</v>
       </c>
       <c r="G54" s="3">
-        <v>551500</v>
+        <v>535500</v>
       </c>
       <c r="H54" s="3">
-        <v>556400</v>
+        <v>528800</v>
       </c>
       <c r="I54" s="3">
-        <v>570000</v>
+        <v>542900</v>
       </c>
       <c r="J54" s="3">
+        <v>551600</v>
+      </c>
+      <c r="K54" s="3">
         <v>596100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>602200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>604300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>378100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>190400</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,47 +3269,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>19000</v>
+        <v>22700</v>
       </c>
       <c r="E57" s="3">
-        <v>20500</v>
+        <v>18300</v>
       </c>
       <c r="F57" s="3">
-        <v>22700</v>
+        <v>2300</v>
       </c>
       <c r="G57" s="3">
-        <v>20800</v>
+        <v>21600</v>
       </c>
       <c r="H57" s="3">
-        <v>18300</v>
+        <v>20000</v>
       </c>
       <c r="I57" s="3">
-        <v>22900</v>
+        <v>17900</v>
       </c>
       <c r="J57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K57" s="3">
         <v>19400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>32300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>36200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14800</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3195,47 +3326,50 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="E58" s="3">
-        <v>3300</v>
+        <v>2900</v>
       </c>
       <c r="F58" s="3">
-        <v>3600</v>
+        <v>3200</v>
       </c>
       <c r="G58" s="3">
-        <v>2900</v>
+        <v>3500</v>
       </c>
       <c r="H58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K58" s="3">
         <v>3200</v>
       </c>
-      <c r="I58" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2800</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3251,47 +3385,50 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>48000</v>
+        <v>50600</v>
       </c>
       <c r="E59" s="3">
-        <v>50300</v>
+        <v>46200</v>
       </c>
       <c r="F59" s="3">
-        <v>53600</v>
+        <v>52600</v>
       </c>
       <c r="G59" s="3">
-        <v>45300</v>
+        <v>51000</v>
       </c>
       <c r="H59" s="3">
-        <v>43300</v>
+        <v>43500</v>
       </c>
       <c r="I59" s="3">
-        <v>42600</v>
+        <v>42300</v>
       </c>
       <c r="J59" s="3">
+        <v>43400</v>
+      </c>
+      <c r="K59" s="3">
         <v>49700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>44400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>49500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>38500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>276600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3307,47 +3444,50 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>70000</v>
+        <v>76100</v>
       </c>
       <c r="E60" s="3">
-        <v>74100</v>
+        <v>67300</v>
       </c>
       <c r="F60" s="3">
-        <v>80000</v>
+        <v>72800</v>
       </c>
       <c r="G60" s="3">
-        <v>69100</v>
+        <v>76000</v>
       </c>
       <c r="H60" s="3">
-        <v>64800</v>
+        <v>66300</v>
       </c>
       <c r="I60" s="3">
-        <v>68700</v>
+        <v>63300</v>
       </c>
       <c r="J60" s="3">
+        <v>66500</v>
+      </c>
+      <c r="K60" s="3">
         <v>72300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>93600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>101900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>66400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>294200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3363,47 +3503,50 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="E61" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F61" s="3">
         <v>4100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H61" s="3">
         <v>4800</v>
       </c>
-      <c r="G61" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>5700</v>
-      </c>
       <c r="I61" s="3">
-        <v>6400</v>
+        <v>5500</v>
       </c>
       <c r="J61" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K61" s="3">
         <v>7200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3419,47 +3562,50 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5600</v>
+        <v>9300</v>
       </c>
       <c r="E62" s="3">
-        <v>5300</v>
+        <v>1700</v>
       </c>
       <c r="F62" s="3">
-        <v>3400</v>
+        <v>1500</v>
       </c>
       <c r="G62" s="3">
-        <v>5800</v>
+        <v>2000</v>
       </c>
       <c r="H62" s="3">
-        <v>7400</v>
+        <v>4300</v>
       </c>
       <c r="I62" s="3">
-        <v>6000</v>
+        <v>5900</v>
       </c>
       <c r="J62" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K62" s="3">
         <v>2100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,47 +3798,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>79100</v>
+        <v>92500</v>
       </c>
       <c r="E66" s="3">
-        <v>83500</v>
+        <v>76100</v>
       </c>
       <c r="F66" s="3">
-        <v>88200</v>
+        <v>82100</v>
       </c>
       <c r="G66" s="3">
-        <v>80000</v>
+        <v>83900</v>
       </c>
       <c r="H66" s="3">
-        <v>77900</v>
+        <v>76700</v>
       </c>
       <c r="I66" s="3">
-        <v>81200</v>
+        <v>76000</v>
       </c>
       <c r="J66" s="3">
+        <v>78500</v>
+      </c>
+      <c r="K66" s="3">
         <v>81600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>103900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>113200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>90700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>318100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3699,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3869,11 +4037,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>44000</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,47 +4116,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-352300</v>
+        <v>-358700</v>
       </c>
       <c r="E72" s="3">
-        <v>-348200</v>
+        <v>-348700</v>
       </c>
       <c r="F72" s="3">
-        <v>-346200</v>
+        <v>-351400</v>
       </c>
       <c r="G72" s="3">
-        <v>-346700</v>
+        <v>-340500</v>
       </c>
       <c r="H72" s="3">
-        <v>-338100</v>
+        <v>-343800</v>
       </c>
       <c r="I72" s="3">
-        <v>-331500</v>
+        <v>-345000</v>
       </c>
       <c r="J72" s="3">
+        <v>-334500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-327300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-313100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-316300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-222600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-200300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,47 +4352,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>464400</v>
+        <v>435100</v>
       </c>
       <c r="E76" s="3">
-        <v>466100</v>
+        <v>446900</v>
       </c>
       <c r="F76" s="3">
-        <v>475300</v>
+        <v>458200</v>
       </c>
       <c r="G76" s="3">
-        <v>471600</v>
+        <v>451600</v>
       </c>
       <c r="H76" s="3">
-        <v>478500</v>
+        <v>452100</v>
       </c>
       <c r="I76" s="3">
-        <v>488900</v>
+        <v>466900</v>
       </c>
       <c r="J76" s="3">
+        <v>473000</v>
+      </c>
+      <c r="K76" s="3">
         <v>514500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>498300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>491100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>287400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-171800</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4225,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F81" s="3">
+        <v>800</v>
+      </c>
+      <c r="G81" s="3">
+        <v>200</v>
+      </c>
+      <c r="H81" s="3">
         <v>-4800</v>
       </c>
-      <c r="E81" s="3">
-        <v>800</v>
-      </c>
-      <c r="F81" s="3">
-        <v>200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-7900</v>
-      </c>
       <c r="I81" s="3">
-        <v>-4000</v>
+        <v>-7700</v>
       </c>
       <c r="J81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-90100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-139100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-111700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1700</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4618,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5000</v>
+        <v>4300</v>
       </c>
       <c r="E83" s="3">
-        <v>4800</v>
+        <v>4400</v>
       </c>
       <c r="F83" s="3">
-        <v>4700</v>
+        <v>-5700</v>
       </c>
       <c r="G83" s="3">
-        <v>4500</v>
+        <v>3400</v>
       </c>
       <c r="H83" s="3">
-        <v>4500</v>
+        <v>4300</v>
       </c>
       <c r="I83" s="3">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="J83" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K83" s="3">
         <v>3800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3500</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
-        <v>4000</v>
-      </c>
       <c r="F89" s="3">
-        <v>16300</v>
+        <v>3900</v>
       </c>
       <c r="G89" s="3">
-        <v>8400</v>
+        <v>15500</v>
       </c>
       <c r="H89" s="3">
-        <v>-3800</v>
+        <v>8100</v>
       </c>
       <c r="I89" s="3">
-        <v>-12800</v>
+        <v>-3700</v>
       </c>
       <c r="J89" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-4500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
-        <v>-12900</v>
+        <v>-200</v>
       </c>
       <c r="G91" s="3">
-        <v>-6800</v>
+        <v>-200</v>
       </c>
       <c r="H91" s="3">
-        <v>-6700</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-200</v>
       </c>
       <c r="O91" s="3">
         <v>-200</v>
       </c>
       <c r="P91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5500</v>
+        <v>-4800</v>
       </c>
       <c r="E94" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4300</v>
       </c>
-      <c r="F94" s="3">
-        <v>-5400</v>
-      </c>
       <c r="G94" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-5200</v>
       </c>
-      <c r="H94" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13500</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,31 +5313,32 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,99 +5547,105 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1000</v>
+        <v>-700</v>
       </c>
       <c r="E100" s="3">
         <v>-900</v>
       </c>
       <c r="F100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G100" s="3">
         <v>-700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>232700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>65400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>18800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3800</v>
+        <v>3400</v>
       </c>
       <c r="E101" s="3">
-        <v>-6600</v>
+        <v>-1800</v>
       </c>
       <c r="F101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>3500</v>
+        <v>-2800</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="J101" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>4100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-4600</v>
+        <v>6600</v>
       </c>
       <c r="E102" s="3">
-        <v>-7800</v>
+        <v>-4400</v>
       </c>
       <c r="F102" s="3">
-        <v>11400</v>
+        <v>-7700</v>
       </c>
       <c r="G102" s="3">
-        <v>5700</v>
+        <v>10800</v>
       </c>
       <c r="H102" s="3">
-        <v>-11400</v>
+        <v>5500</v>
       </c>
       <c r="I102" s="3">
-        <v>-23400</v>
+        <v>-11200</v>
       </c>
       <c r="J102" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-22500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>224000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>50800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3500</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
